--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008412105359976642</v>
       </c>
       <c r="C2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>9789505</v>
+        <v>4791621</v>
       </c>
       <c r="L2" t="n">
-        <v>6235245</v>
+        <v>2983908</v>
       </c>
       <c r="M2" t="n">
-        <v>1673957</v>
+        <v>780721</v>
       </c>
       <c r="N2" t="n">
-        <v>107773</v>
+        <v>45049</v>
       </c>
       <c r="O2" t="n">
-        <v>967260</v>
+        <v>458919</v>
       </c>
       <c r="P2" t="n">
-        <v>371826</v>
+        <v>179516</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999980926513672</v>
+        <v>0.9999982714653015</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9781314134597778</v>
+        <v>0.9570696949958801</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9308509826660156</v>
+        <v>0.8913102746009827</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9320493936538696</v>
+        <v>0.8701371550559998</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8505820631980896</v>
+        <v>0.7123723030090332</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9493029713630676</v>
+        <v>0.9009435176849365</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9662988781929016</v>
+        <v>0.9329044222831726</v>
       </c>
       <c r="X2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="AG2" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AH2" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AI2" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567450881004333</v>
+        <v>0.9567357897758484</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112150073051453</v>
+        <v>0.9112488627433777</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582985401153564</v>
+        <v>0.8582139611244202</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627530455589294</v>
+        <v>0.6625582575798035</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020664095878601</v>
+        <v>0.9019841551780701</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -792,130 +792,130 @@
         <v>0.002017379093236049</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>9789505</v>
+        <v>4791621</v>
       </c>
       <c r="E3" t="n">
-        <v>280997</v>
+        <v>240035</v>
       </c>
       <c r="F3" t="n">
-        <v>1976</v>
+        <v>1927</v>
       </c>
       <c r="G3" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I3" t="n">
         <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>20033220</v>
+        <v>10016611</v>
       </c>
       <c r="K3" t="n">
-        <v>22367295</v>
+        <v>11080529</v>
       </c>
       <c r="L3" t="n">
-        <v>25681340</v>
+        <v>12706378</v>
       </c>
       <c r="M3" t="n">
-        <v>30673995</v>
+        <v>15281270</v>
       </c>
       <c r="N3" t="n">
-        <v>32462199</v>
+        <v>16222347</v>
       </c>
       <c r="O3" t="n">
-        <v>31589786</v>
+        <v>15770170</v>
       </c>
       <c r="P3" t="n">
-        <v>32259687</v>
+        <v>16123407</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9718524813652039</v>
+        <v>0.9518254995346069</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9571083188056946</v>
+        <v>0.9154909253120422</v>
       </c>
       <c r="T3" t="n">
-        <v>0.898447573184967</v>
+        <v>0.8378524780273438</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6052317023277283</v>
+        <v>0.5058048367500305</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9503831267356873</v>
+        <v>0.9016568660736084</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9619216322898865</v>
+        <v>0.9287776350975037</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="Z3" t="n">
-        <v>395630</v>
+        <v>197858</v>
       </c>
       <c r="AA3" t="n">
-        <v>17032</v>
+        <v>8531</v>
       </c>
       <c r="AB3" t="n">
-        <v>13547</v>
+        <v>6780</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20033244</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>22150033</v>
+        <v>11077458</v>
       </c>
       <c r="AG3" t="n">
-        <v>25566849</v>
+        <v>12781334</v>
       </c>
       <c r="AH3" t="n">
-        <v>30532165</v>
+        <v>15265735</v>
       </c>
       <c r="AI3" t="n">
-        <v>32421126</v>
+        <v>16210502</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31541812</v>
+        <v>15770758</v>
       </c>
       <c r="AK3" t="n">
-        <v>32246147</v>
+        <v>16123064</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576732516288757</v>
+        <v>0.9576404094696045</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100743532180786</v>
+        <v>0.9101204872131348</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578290939331055</v>
+        <v>0.8577921390533447</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66222083568573</v>
+        <v>0.6621193885803223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016799926757812</v>
+        <v>0.9016509652137756</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -929,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>203483</v>
+        <v>200386</v>
       </c>
       <c r="E4" t="n">
-        <v>6235245</v>
+        <v>2983908</v>
       </c>
       <c r="F4" t="n">
-        <v>73649</v>
+        <v>72767</v>
       </c>
       <c r="G4" t="n">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H4" t="n">
         <v>1152</v>
@@ -947,109 +947,109 @@
         <v>44</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>218869</v>
+        <v>214933</v>
       </c>
       <c r="L4" t="n">
-        <v>463190</v>
+        <v>363869</v>
       </c>
       <c r="M4" t="n">
-        <v>122039</v>
+        <v>116518</v>
       </c>
       <c r="N4" t="n">
-        <v>18932</v>
+        <v>18189</v>
       </c>
       <c r="O4" t="n">
-        <v>51656</v>
+        <v>50457</v>
       </c>
       <c r="P4" t="n">
-        <v>12968</v>
+        <v>12911</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999990463256836</v>
+        <v>0.9999991059303284</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9749818444252014</v>
+        <v>0.9544403553009033</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9437971115112305</v>
+        <v>0.9032387733459473</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9149400591850281</v>
+        <v>0.8536896705627441</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7072322964668274</v>
+        <v>0.5915746688842773</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9498427510261536</v>
+        <v>0.9013000726699829</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9641053080558777</v>
+        <v>0.9308364391326904</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>407180</v>
+        <v>203532</v>
       </c>
       <c r="Z4" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AA4" t="n">
-        <v>165287</v>
+        <v>82724</v>
       </c>
       <c r="AB4" t="n">
-        <v>10949</v>
+        <v>5477</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>436131</v>
+        <v>218004</v>
       </c>
       <c r="AG4" t="n">
-        <v>577681</v>
+        <v>288913</v>
       </c>
       <c r="AH4" t="n">
-        <v>263869</v>
+        <v>132053</v>
       </c>
       <c r="AI4" t="n">
-        <v>60005</v>
+        <v>30034</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99630</v>
+        <v>49869</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572089314460754</v>
+        <v>0.9571878910064697</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106443524360657</v>
+        <v>0.9106842875480652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8580637574195862</v>
+        <v>0.8580030798912048</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624868512153625</v>
+        <v>0.6623387336730957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018731117248535</v>
+        <v>0.9018175005912781</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
@@ -1059,16 +1059,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8515</v>
+        <v>8064</v>
       </c>
       <c r="E5" t="n">
-        <v>142017</v>
+        <v>104693</v>
       </c>
       <c r="F5" t="n">
-        <v>1673957</v>
+        <v>780721</v>
       </c>
       <c r="G5" t="n">
-        <v>8974</v>
+        <v>8631</v>
       </c>
       <c r="H5" t="n">
         <v>29125</v>
@@ -1080,131 +1080,131 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>283531</v>
+        <v>242517</v>
       </c>
       <c r="L5" t="n">
-        <v>279425</v>
+        <v>275445</v>
       </c>
       <c r="M5" t="n">
-        <v>189209</v>
+        <v>151091</v>
       </c>
       <c r="N5" t="n">
-        <v>70296</v>
+        <v>44015</v>
       </c>
       <c r="O5" t="n">
-        <v>50498</v>
+        <v>50054</v>
       </c>
       <c r="P5" t="n">
-        <v>14719</v>
+        <v>13766</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999992847442627</v>
+        <v>0.9999993443489075</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9846168756484985</v>
+        <v>0.9719864726066589</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9772616624832153</v>
+        <v>0.960849404335022</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9904698133468628</v>
+        <v>0.9836120009422302</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9972679018974304</v>
+        <v>0.9961907267570496</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9968721270561218</v>
+        <v>0.9938448667526245</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9991522431373596</v>
+        <v>0.9983663558959961</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15974</v>
+        <v>7983</v>
       </c>
       <c r="Z5" t="n">
-        <v>169599</v>
+        <v>84824</v>
       </c>
       <c r="AA5" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AB5" t="n">
-        <v>19854</v>
+        <v>9943</v>
       </c>
       <c r="AC5" t="n">
-        <v>58195</v>
+        <v>29128</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>426359</v>
+        <v>213244</v>
       </c>
       <c r="AG5" t="n">
-        <v>585836</v>
+        <v>292949</v>
       </c>
       <c r="AH5" t="n">
-        <v>264888</v>
+        <v>132511</v>
       </c>
       <c r="AI5" t="n">
-        <v>60148</v>
+        <v>30093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100066</v>
+        <v>50057</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735912084579468</v>
+        <v>0.9735910296440125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643740057945251</v>
+        <v>0.9643676280975342</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838098883628845</v>
+        <v>0.9837985038757324</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210225105286</v>
+        <v>0.9963179230690002</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938854575157166</v>
+        <v>0.9938806891441345</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983761310577393</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6812</v>
+        <v>6431</v>
       </c>
       <c r="E6" t="n">
-        <v>39275</v>
+        <v>18249</v>
       </c>
       <c r="F6" t="n">
-        <v>16486</v>
+        <v>11903</v>
       </c>
       <c r="G6" t="n">
-        <v>107773</v>
+        <v>45049</v>
       </c>
       <c r="H6" t="n">
-        <v>7336</v>
+        <v>7054</v>
       </c>
       <c r="I6" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12866</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>10669</v>
+        <v>5341</v>
       </c>
       <c r="AA6" t="n">
-        <v>21709</v>
+        <v>10859</v>
       </c>
       <c r="AB6" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AC6" t="n">
-        <v>13942</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
         <v>801</v>
       </c>
       <c r="F7" t="n">
-        <v>29600</v>
+        <v>29597</v>
       </c>
       <c r="G7" t="n">
-        <v>8107</v>
+        <v>7722</v>
       </c>
       <c r="H7" t="n">
-        <v>967260</v>
+        <v>458919</v>
       </c>
       <c r="I7" t="n">
-        <v>11965</v>
+        <v>11910</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1621</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>59181</v>
+        <v>29609</v>
       </c>
       <c r="AB7" t="n">
-        <v>15125</v>
+        <v>7569</v>
       </c>
       <c r="AC7" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="F8" t="n">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="G8" t="n">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="H8" t="n">
-        <v>13977</v>
+        <v>13061</v>
       </c>
       <c r="I8" t="n">
-        <v>371826</v>
+        <v>179516</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
